--- a/artfynd/A 61089-2025 artfynd.xlsx
+++ b/artfynd/A 61089-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126837059</v>
       </c>
       <c r="B2" t="n">
-        <v>78777</v>
+        <v>78770</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>126837058</v>
       </c>
       <c r="B3" t="n">
-        <v>78777</v>
+        <v>78770</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>126837060</v>
       </c>
       <c r="B4" t="n">
-        <v>78777</v>
+        <v>78770</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>126837047</v>
       </c>
       <c r="B5" t="n">
-        <v>56853</v>
+        <v>56849</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>126837039</v>
       </c>
       <c r="B6" t="n">
-        <v>79636</v>
+        <v>79629</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
         <v>126837050</v>
       </c>
       <c r="B7" t="n">
-        <v>57821</v>
+        <v>57817</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 61089-2025 artfynd.xlsx
+++ b/artfynd/A 61089-2025 artfynd.xlsx
@@ -1296,7 +1296,7 @@
         <v>130340419</v>
       </c>
       <c r="B8" t="n">
-        <v>57985</v>
+        <v>58011</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 61089-2025 artfynd.xlsx
+++ b/artfynd/A 61089-2025 artfynd.xlsx
@@ -1296,7 +1296,7 @@
         <v>130340419</v>
       </c>
       <c r="B8" t="n">
-        <v>58011</v>
+        <v>58013</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 61089-2025 artfynd.xlsx
+++ b/artfynd/A 61089-2025 artfynd.xlsx
@@ -1296,7 +1296,7 @@
         <v>130340419</v>
       </c>
       <c r="B8" t="n">
-        <v>58013</v>
+        <v>58021</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 61089-2025 artfynd.xlsx
+++ b/artfynd/A 61089-2025 artfynd.xlsx
@@ -1296,7 +1296,7 @@
         <v>130340419</v>
       </c>
       <c r="B8" t="n">
-        <v>58021</v>
+        <v>58022</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 61089-2025 artfynd.xlsx
+++ b/artfynd/A 61089-2025 artfynd.xlsx
@@ -1296,7 +1296,7 @@
         <v>130340419</v>
       </c>
       <c r="B8" t="n">
-        <v>58022</v>
+        <v>58023</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 61089-2025 artfynd.xlsx
+++ b/artfynd/A 61089-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126837059</v>
+        <v>126837039</v>
       </c>
       <c r="B2" t="n">
-        <v>78777</v>
+        <v>79946</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>681537</v>
+        <v>681524</v>
       </c>
       <c r="R2" t="n">
-        <v>7086618</v>
+        <v>7086643</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,45 +776,57 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126837058</v>
+        <v>126837047</v>
       </c>
       <c r="B3" t="n">
-        <v>78777</v>
+        <v>57141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>681512</v>
+        <v>681486</v>
       </c>
       <c r="R3" t="n">
-        <v>7086618</v>
+        <v>7086660</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126837060</v>
+        <v>126837050</v>
       </c>
       <c r="B4" t="n">
-        <v>78777</v>
+        <v>58114</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>681513</v>
+        <v>681537</v>
       </c>
       <c r="R4" t="n">
-        <v>7086681</v>
+        <v>7086618</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,60 +990,56 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126837047</v>
+        <v>130340419</v>
       </c>
       <c r="B5" t="n">
-        <v>56853</v>
+        <v>58114</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Rödtjärnliden, Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>681486</v>
+        <v>681528</v>
       </c>
       <c r="R5" t="n">
-        <v>7086660</v>
+        <v>7086701</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1058,16 +1066,26 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG5" t="b">
         <v>0</v>
@@ -1080,21 +1098,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126837039</v>
+        <v>126837058</v>
       </c>
       <c r="B6" t="n">
-        <v>79636</v>
+        <v>79085</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1102,21 +1116,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1126,10 +1140,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>681524</v>
+        <v>681512</v>
       </c>
       <c r="R6" t="n">
-        <v>7086643</v>
+        <v>7086618</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1192,10 +1206,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126837050</v>
+        <v>126837059</v>
       </c>
       <c r="B7" t="n">
-        <v>57821</v>
+        <v>79085</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1203,21 +1217,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1293,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130340419</v>
+        <v>126837060</v>
       </c>
       <c r="B8" t="n">
-        <v>58023</v>
+        <v>79085</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1304,45 +1318,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Rödtjärnliden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>681528</v>
+        <v>681513</v>
       </c>
       <c r="R8" t="n">
-        <v>7086701</v>
+        <v>7086681</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1369,26 +1375,16 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="b">
         <v>0</v>
@@ -1401,10 +1397,115 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>126837061</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Rödtjärnliden, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>681495</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7086737</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
           <t>Liam Sebestyén</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61089-2025 artfynd.xlsx
+++ b/artfynd/A 61089-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126837039</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126837047</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126837050</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1102,6 +1122,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130340419</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1203,6 +1228,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126837058</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1304,6 +1334,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126837059</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1405,6 +1440,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126837060</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1506,8 +1546,23 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126837061</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>